--- a/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_m_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_m_2019.xlsx
@@ -282,7 +282,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 09:16</t>
+    <t xml:space="preserve">2026-10-05 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
